--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104642_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104642_W21.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2935</v>
+        <v>6.2886</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9307</v>
+        <v>6.7257</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6372</v>
+        <v>-0.4371</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4674</v>
+        <v>5.456</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.3505</v>
+        <v>-2.3521</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8179</v>
+        <v>7.8081</v>
       </c>
       <c r="J2" t="n">
-        <v>7.7393</v>
+        <v>7.6879</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1367</v>
+        <v>-1.1591</v>
       </c>
       <c r="L2" t="n">
-        <v>8.875999999999999</v>
+        <v>8.847</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.2719</v>
+        <v>-2.232</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2139</v>
+        <v>-1.1931</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0581</v>
+        <v>-1.0389</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.4422</v>
+        <v>-1.4437</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.8086</v>
+        <v>-0.9622000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.4815</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>E. SANMARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0892</v>
+        <v>1.2499</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4897</v>
+        <v>0.2772</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5995</v>
+        <v>0.9727</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7849</v>
+        <v>1.0905</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4517</v>
+        <v>-0.164</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3333</v>
+        <v>1.2544</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8907</v>
+        <v>0.2007</v>
       </c>
       <c r="K3" t="n">
-        <v>0.107</v>
+        <v>0.0517</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7837</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1057</v>
+        <v>0.8898</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3446</v>
+        <v>-0.2157</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4504</v>
+        <v>1.1055</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8221</v>
+        <v>0.3172</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3852</v>
+        <v>0.0765</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4369</v>
+        <v>0.2407</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1568</v>
+        <v>-0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4822</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.639</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9045</v>
+        <v>0.5056</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5549</v>
+        <v>1.9264</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6504</v>
+        <v>-1.4208</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0284</v>
+        <v>-0.4249</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8122</v>
+        <v>-1.1889</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.764</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4577</v>
+        <v>0.9208</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6367</v>
+        <v>-0.4417</v>
       </c>
       <c r="L4" t="n">
-        <v>0.821</v>
+        <v>1.3624</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4861</v>
+        <v>-1.3457</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4489</v>
+        <v>-0.7472</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0372</v>
+        <v>-0.5984</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1183</v>
+        <v>-0.159</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3902</v>
+        <v>-0.0838</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2719</v>
+        <v>-0.0752</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. SANMARTIN</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8452</v>
+        <v>-0.0625</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1466</v>
+        <v>0.1252</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9918</v>
+        <v>-0.1877</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0813</v>
+        <v>-0.3879</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1689</v>
+        <v>0.7356</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2502</v>
+        <v>-1.1235</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2012</v>
+        <v>0.0523</v>
       </c>
       <c r="K5" t="n">
-        <v>0.052</v>
+        <v>0.6787</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1493</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.88</v>
+        <v>-0.4402</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2209</v>
+        <v>0.0568</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1009</v>
+        <v>-0.497</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.7932</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3478</v>
+        <v>-0.4718</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2725</v>
+        <v>-0.3213</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1607</v>
+        <v>-0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2579</v>
+        <v>-0.1926</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4467</v>
+        <v>1.7697</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1888</v>
+        <v>-1.9622</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3751</v>
+        <v>-0.0277</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7418</v>
+        <v>-0.8237</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1169</v>
+        <v>0.796</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08790000000000001</v>
+        <v>1.4323</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6958</v>
+        <v>0.613</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6079</v>
+        <v>0.8192</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.463</v>
+        <v>-1.4599</v>
       </c>
       <c r="N6" t="n">
-        <v>0.046</v>
+        <v>-1.4367</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.509</v>
+        <v>-0.0232</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4745</v>
+        <v>-0.986</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1875</v>
+        <v>-0.3651</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.287</v>
+        <v>-0.6209</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7071</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5463</v>
+        <v>0.7025</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0061</v>
+        <v>-0.4393</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4121</v>
+        <v>-0.4131</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.406</v>
+        <v>-0.0261</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4184</v>
+        <v>0.7924</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1861</v>
+        <v>0.451</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.3415</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9455</v>
+        <v>0.8747</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4298</v>
+        <v>0.0927</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3753</v>
+        <v>0.782</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3639</v>
+        <v>-0.0822</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7563</v>
+        <v>0.3583</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6077</v>
+        <v>-0.4405</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6681</v>
+        <v>1.295</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6261</v>
+        <v>0.5152</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0421</v>
+        <v>0.7798</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>-1.1609</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>0.4733</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6738</v>
+        <v>-0.9474</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7079</v>
+        <v>-0.2462</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9659</v>
+        <v>-0.7012</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4542</v>
+        <v>1.4565</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4386</v>
+        <v>0.4421</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0156</v>
+        <v>1.0144</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7741</v>
+        <v>0.7667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.329</v>
+        <v>0.3275</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M8" t="n">
-        <v>0.68</v>
+        <v>0.6898</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3478</v>
+        <v>0.1253</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3926</v>
+        <v>-0.1438</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8137</v>
+        <v>-1.6302</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3578</v>
+        <v>-1.244</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4559</v>
+        <v>-0.3862</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.8915</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3449</v>
+        <v>-0.3419</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5517</v>
+        <v>-0.5496</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9513</v>
+        <v>-0.946</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2365</v>
+        <v>-0.0558</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3592</v>
+        <v>-2.4422</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9391</v>
+        <v>-2.2495</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4201</v>
+        <v>-0.1927</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1468</v>
+        <v>-1.1361</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3551</v>
+        <v>-0.3452</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7917</v>
+        <v>-0.791</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2152</v>
+        <v>-0.237</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3813</v>
+        <v>-0.3954</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9316</v>
+        <v>-0.8992</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.029</v>
+        <v>-0.1255</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1815</v>
+        <v>-0.1004</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2105</v>
+        <v>-0.0251</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6146</v>
+        <v>-3.913</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6819</v>
+        <v>-2.0063</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9327</v>
+        <v>-1.9067</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.27</v>
+        <v>-5.2683</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4228</v>
+        <v>-3.418</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8472</v>
+        <v>-1.8502</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.5521</v>
+        <v>-3.5795</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2725</v>
+        <v>-2.2827</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2796</v>
+        <v>-1.2967</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7179</v>
+        <v>-1.6888</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7833</v>
+        <v>-1.0709</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1119</v>
+        <v>-0.1701</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8953</v>
+        <v>-0.9008</v>
       </c>
       <c r="V11" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.731</v>
+        <v>-4.5151</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4677</v>
+        <v>-4.7277</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2633</v>
+        <v>0.2126</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0361</v>
+        <v>-2.0342</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4661</v>
+        <v>-0.4626</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.57</v>
+        <v>-1.5716</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8082</v>
+        <v>-1.8377</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1181</v>
+        <v>-0.1314</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.6901</v>
+        <v>-1.7063</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.228</v>
+        <v>-0.1965</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3754</v>
+        <v>-1.1637</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3912</v>
+        <v>-0.6137</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9842</v>
+        <v>-0.5501</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.795899999999999</v>
+        <v>-6.0982</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.466899999999999</v>
+        <v>-0.06259999999999888</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.329</v>
+        <v>-6.0354</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.383699999999999</v>
+        <v>-1.3752</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.4745</v>
+        <v>-7.467700000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>6.090899999999997</v>
+        <v>6.092499999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>6.575500000000003</v>
+        <v>6.335700000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.9532</v>
+        <v>-2.0757</v>
       </c>
       <c r="L13" t="n">
-        <v>8.5288</v>
+        <v>8.411</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.9594</v>
+        <v>-7.710900000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.521500000000001</v>
+        <v>-5.3923</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.438</v>
+        <v>-2.3185</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2683</v>
+        <v>2.276300000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.105399999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8843</v>
+        <v>-4.2041</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9184</v>
+        <v>-2.2105</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9661</v>
+        <v>-1.9936</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.795800000000001</v>
+        <v>-2.7951</v>
       </c>
       <c r="W13" t="n">
-        <v>4.9495</v>
+        <v>4.9175</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.7453</v>
+        <v>-7.712600000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8683</v>
+        <v>4.4531</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4795</v>
+        <v>1.5113</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3888</v>
+        <v>2.9418</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2467</v>
+        <v>3.0234</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3983</v>
+        <v>1.6482</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.645</v>
+        <v>1.3751</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3859</v>
+        <v>1.37</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3086</v>
+        <v>0.9308</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.4392</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1392</v>
+        <v>1.6534</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5676</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1811</v>
+        <v>0.7469</v>
       </c>
       <c r="T14" t="n">
-        <v>1.612</v>
+        <v>0.1414</v>
       </c>
       <c r="U14" t="n">
-        <v>1.569</v>
+        <v>0.6055</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8163</v>
+        <v>3.2519</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9296</v>
+        <v>1.3988</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8867</v>
+        <v>1.8531</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0121</v>
+        <v>-0.2392</v>
       </c>
       <c r="H15" t="n">
-        <v>1.642</v>
+        <v>0.3964</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3701</v>
+        <v>-0.6357</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3802</v>
+        <v>-0.4031</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9351</v>
+        <v>-0.321</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4451</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6319</v>
+        <v>0.1639</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O15" t="n">
-        <v>0.925</v>
+        <v>-0.5535</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1237</v>
+        <v>1.561</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4506</v>
+        <v>0.5547</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5743</v>
+        <v>1.0063</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0867</v>
+        <v>2.4514</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5515</v>
+        <v>0.9846</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5352</v>
+        <v>1.4668</v>
       </c>
       <c r="G16" t="n">
-        <v>4.8048</v>
+        <v>4.8007</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2641</v>
+        <v>3.2573</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5407</v>
+        <v>1.5434</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4228</v>
+        <v>4.3947</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7463</v>
+        <v>2.7267</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M16" t="n">
-        <v>0.382</v>
+        <v>0.406</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4576</v>
+        <v>0.8375</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2419</v>
+        <v>0.232</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6995</v>
+        <v>0.6055</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0834</v>
+        <v>2.2701</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2933</v>
+        <v>1.1313</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7901</v>
+        <v>1.1389</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7788</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.371</v>
+        <v>0.3596</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7459</v>
+        <v>0.6975</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2882</v>
+        <v>-0.3145</v>
       </c>
       <c r="L17" t="n">
-        <v>1.034</v>
+        <v>1.012</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0329</v>
+        <v>0.0641</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6263</v>
+        <v>-0.61</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7168</v>
+        <v>0.9152</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7743</v>
+        <v>0.6614</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0575</v>
+        <v>0.2537</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0081</v>
+        <v>1.6403</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1363</v>
+        <v>2.9597</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1282</v>
+        <v>-1.3194</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4387</v>
+        <v>0.1282</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3578</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7965</v>
+        <v>0.1939</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5707</v>
+        <v>-0.0169</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1704</v>
+        <v>-0.1659</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5998</v>
+        <v>0.1489</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0094</v>
+        <v>0.1451</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1874</v>
+        <v>0.1002</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1967</v>
+        <v>0.0449</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5395</v>
+        <v>0.2845</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6998</v>
+        <v>0.253</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1603</v>
+        <v>0.0316</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>2.7237</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6647</v>
+        <v>1.2746</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0972</v>
+        <v>2.0594</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4325</v>
+        <v>-0.7849</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1302</v>
+        <v>-0.4302</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0591</v>
+        <v>1.3585</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1893</v>
+        <v>-1.7887</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0035</v>
+        <v>0.5547</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1527</v>
+        <v>1.1581</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1493</v>
+        <v>-0.6035</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1337</v>
+        <v>-0.9849</v>
       </c>
       <c r="N19" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.2003</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04</v>
+        <v>-1.1852</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3076</v>
+        <v>0.7943</v>
       </c>
       <c r="T19" t="n">
-        <v>0.369</v>
+        <v>0.6429</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0614</v>
+        <v>0.1513</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.7317</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9431</v>
+        <v>1.008</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7063</v>
+        <v>0.7047</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2368</v>
+        <v>0.3033</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6745</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1544</v>
+        <v>-0.1523</v>
       </c>
       <c r="I20" t="n">
-        <v>0.829</v>
+        <v>0.8282</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7063</v>
+        <v>0.7047</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8129</v>
+        <v>-0.389</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4125</v>
+        <v>-0.0675</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4004</v>
+        <v>-0.3215</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1938</v>
+        <v>-1.1859</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2322</v>
+        <v>0.2381</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.426</v>
+        <v>-1.424</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1224</v>
+        <v>0.1164</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3117</v>
+        <v>0.3103</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3162</v>
+        <v>-1.3023</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7779</v>
+        <v>-0.3624</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6965</v>
+        <v>-1.8066</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8108</v>
+        <v>-0.741</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1143</v>
+        <v>-1.0655</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2444</v>
+        <v>1.6274</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2928</v>
+        <v>0.1635</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.5372</v>
+        <v>1.4638</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9791</v>
+        <v>2.941</v>
       </c>
       <c r="K22" t="n">
-        <v>1.42</v>
+        <v>0.1789</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.3991</v>
+        <v>2.7621</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2653</v>
+        <v>-1.3136</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1272</v>
+        <v>-0.0154</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1381</v>
+        <v>-1.2982</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.323</v>
+        <v>0.1383</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5293</v>
+        <v>-0.2189</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2063</v>
+        <v>0.3572</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2249</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2249</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2023</v>
+        <v>-1.983</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6269</v>
+        <v>-2.1878</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5754</v>
+        <v>0.2048</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6341</v>
+        <v>-2.2446</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1601</v>
+        <v>1.2979</v>
       </c>
       <c r="I23" t="n">
-        <v>1.474</v>
+        <v>-3.5425</v>
       </c>
       <c r="J23" t="n">
-        <v>2.9815</v>
+        <v>-1.0004</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1936</v>
+        <v>1.4134</v>
       </c>
       <c r="L23" t="n">
-        <v>2.7879</v>
+        <v>-2.4138</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3475</v>
+        <v>-1.2442</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0335</v>
+        <v>-0.1155</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.314</v>
+        <v>-1.1287</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2731</v>
+        <v>0.0324</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1644</v>
+        <v>0.1784</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8913</v>
+        <v>-0.146</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1607</v>
+        <v>0.2292</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="24">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.634</v>
+        <v>-2.5086</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.7589</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7604</v>
+        <v>-1.7497</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6966</v>
+        <v>-1.6971</v>
       </c>
       <c r="H24" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7486</v>
+        <v>-1.7488</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="K24" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2326,22 +2326,22 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0696</v>
+        <v>0.0697</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3291</v>
+        <v>-2.8672</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.141</v>
+        <v>-0.9593</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1881</v>
+        <v>-1.9079</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.8304</v>
+        <v>-3.8447</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0822</v>
+        <v>-1.0855</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.7482</v>
+        <v>-2.7593</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8675</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5928</v>
+        <v>-0.6108</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.2747</v>
+        <v>-0.299</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.9629</v>
+        <v>-2.935</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.4735</v>
+        <v>-2.4603</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6859</v>
+        <v>-0.1998</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3266</v>
+        <v>-0.0887</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3593</v>
+        <v>-0.1111</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6.795799999999996</v>
+        <v>6.795</v>
       </c>
       <c r="E26" t="n">
-        <v>6.328999999999999</v>
+        <v>6.0353</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4668999999999994</v>
+        <v>0.7598000000000009</v>
       </c>
       <c r="G26" t="n">
-        <v>1.3839</v>
+        <v>1.375500000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>7.474599999999999</v>
+        <v>7.467700000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.0906</v>
+        <v>-6.092700000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>7.959399999999999</v>
+        <v>7.7109</v>
       </c>
       <c r="K26" t="n">
-        <v>5.5214</v>
+        <v>5.3922</v>
       </c>
       <c r="L26" t="n">
-        <v>2.4379</v>
+        <v>2.3186</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.5756</v>
+        <v>-6.335599999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>1.9532</v>
+        <v>2.0754</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.5288</v>
+        <v>-8.411000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2684</v>
+        <v>-2.276299999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.3416</v>
+        <v>-11.3815</v>
       </c>
       <c r="R26" t="n">
-        <v>9.073399999999999</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>4.884499999999999</v>
+        <v>4.9012</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9662</v>
+        <v>1.9935</v>
       </c>
       <c r="U26" t="n">
-        <v>2.918299999999999</v>
+        <v>2.9076</v>
       </c>
       <c r="V26" t="n">
-        <v>2.7959</v>
+        <v>2.795</v>
       </c>
       <c r="W26" t="n">
-        <v>7.7453</v>
+        <v>7.712700000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.9494</v>
+        <v>-4.9175</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104642_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104642_W21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.712600000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104642_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-4.9175</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
